--- a/STM32_WeiDongShan/DMA/DMA_study_软件履历表.xlsx
+++ b/STM32_WeiDongShan/DMA/DMA_study_软件履历表.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MCU_Study\stm32\11_3_SPI_W25Q64\STM32_Study\SPI_W25QXX\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MCU_Study\stm32\11_3_SPI_W25Q64\STM32_Study\STM32_WeiDongShan\ADC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B6B33CF-B36F-4206-8367-CE8959873A51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD581355-EFE8-4DE0-A0EA-3C14ADA69C2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>版本</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -40,32 +40,6 @@
   </si>
   <si>
     <t>备注</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>v0.0.0.1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>在I2C oled代码基础上创建软件读取W25Q64的spi代码 并且能够读取flash厂家和芯片id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>夏天豪</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>v0.0.0.2</t>
-  </si>
-  <si>
-    <t>增加硬件spi内容</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>v0.0.0.3</t>
-  </si>
-  <si>
-    <t>增加硬NM25Q128 SPI配置 且读取到oled</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -431,13 +405,9 @@
       <c r="W1" s="1"/>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
-        <v>4</v>
-      </c>
+      <c r="A2" s="1"/>
       <c r="B2" s="1"/>
-      <c r="C2" s="1" t="s">
-        <v>5</v>
-      </c>
+      <c r="C2" s="1"/>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
@@ -449,9 +419,7 @@
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
       <c r="N2" s="1"/>
-      <c r="O2" s="1" t="s">
-        <v>6</v>
-      </c>
+      <c r="O2" s="1"/>
       <c r="P2" s="1"/>
       <c r="Q2" s="1"/>
       <c r="R2" s="1"/>
@@ -462,13 +430,9 @@
       <c r="W2" s="1"/>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
-        <v>7</v>
-      </c>
+      <c r="A3" s="1"/>
       <c r="B3" s="1"/>
-      <c r="C3" s="1" t="s">
-        <v>8</v>
-      </c>
+      <c r="C3" s="1"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
@@ -480,9 +444,7 @@
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
       <c r="N3" s="1"/>
-      <c r="O3" s="1" t="s">
-        <v>6</v>
-      </c>
+      <c r="O3" s="1"/>
       <c r="P3" s="1"/>
       <c r="Q3" s="1"/>
       <c r="R3" s="1"/>
@@ -493,13 +455,9 @@
       <c r="W3" s="1"/>
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A4" s="1" t="s">
-        <v>9</v>
-      </c>
+      <c r="A4" s="1"/>
       <c r="B4" s="1"/>
-      <c r="C4" s="1" t="s">
-        <v>10</v>
-      </c>
+      <c r="C4" s="1"/>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
@@ -511,9 +469,7 @@
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
       <c r="N4" s="1"/>
-      <c r="O4" s="1" t="s">
-        <v>6</v>
-      </c>
+      <c r="O4" s="1"/>
       <c r="P4" s="1"/>
       <c r="Q4" s="1"/>
       <c r="R4" s="1"/>
@@ -1700,51 +1656,141 @@
     </row>
   </sheetData>
   <mergeCells count="204">
-    <mergeCell ref="R49:W49"/>
-    <mergeCell ref="R50:W50"/>
-    <mergeCell ref="R51:W51"/>
-    <mergeCell ref="R43:W43"/>
-    <mergeCell ref="R44:W44"/>
-    <mergeCell ref="R45:W45"/>
-    <mergeCell ref="R46:W46"/>
-    <mergeCell ref="R47:W47"/>
-    <mergeCell ref="R48:W48"/>
-    <mergeCell ref="R37:W37"/>
-    <mergeCell ref="R38:W38"/>
-    <mergeCell ref="R39:W39"/>
-    <mergeCell ref="R40:W40"/>
-    <mergeCell ref="R41:W41"/>
-    <mergeCell ref="R42:W42"/>
-    <mergeCell ref="R31:W31"/>
-    <mergeCell ref="R32:W32"/>
-    <mergeCell ref="R33:W33"/>
-    <mergeCell ref="R34:W34"/>
-    <mergeCell ref="R35:W35"/>
-    <mergeCell ref="R36:W36"/>
-    <mergeCell ref="R25:W25"/>
-    <mergeCell ref="R26:W26"/>
-    <mergeCell ref="R27:W27"/>
-    <mergeCell ref="R28:W28"/>
-    <mergeCell ref="R29:W29"/>
-    <mergeCell ref="R30:W30"/>
-    <mergeCell ref="R19:W19"/>
-    <mergeCell ref="R20:W20"/>
-    <mergeCell ref="R21:W21"/>
-    <mergeCell ref="R22:W22"/>
-    <mergeCell ref="R23:W23"/>
-    <mergeCell ref="R24:W24"/>
-    <mergeCell ref="R13:W13"/>
-    <mergeCell ref="R14:W14"/>
-    <mergeCell ref="R15:W15"/>
-    <mergeCell ref="R16:W16"/>
-    <mergeCell ref="R17:W17"/>
-    <mergeCell ref="R18:W18"/>
-    <mergeCell ref="R7:W7"/>
-    <mergeCell ref="R8:W8"/>
-    <mergeCell ref="R9:W9"/>
-    <mergeCell ref="R10:W10"/>
-    <mergeCell ref="R11:W11"/>
-    <mergeCell ref="R12:W12"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:N1"/>
+    <mergeCell ref="O1:Q1"/>
+    <mergeCell ref="R1:W1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C2:N2"/>
+    <mergeCell ref="C3:N3"/>
+    <mergeCell ref="C4:N4"/>
+    <mergeCell ref="C5:N5"/>
+    <mergeCell ref="C6:N6"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="C7:N7"/>
+    <mergeCell ref="C8:N8"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="A42:B42"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C9:N9"/>
+    <mergeCell ref="C10:N10"/>
+    <mergeCell ref="C11:N11"/>
+    <mergeCell ref="C12:N12"/>
+    <mergeCell ref="C13:N13"/>
+    <mergeCell ref="C14:N14"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="A50:B50"/>
+    <mergeCell ref="A51:B51"/>
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="A46:B46"/>
+    <mergeCell ref="A47:B47"/>
+    <mergeCell ref="A48:B48"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="C21:N21"/>
+    <mergeCell ref="C22:N22"/>
+    <mergeCell ref="C23:N23"/>
+    <mergeCell ref="C24:N24"/>
+    <mergeCell ref="C25:N25"/>
+    <mergeCell ref="C26:N26"/>
+    <mergeCell ref="C51:N51"/>
+    <mergeCell ref="O2:Q2"/>
+    <mergeCell ref="O3:Q3"/>
+    <mergeCell ref="O4:Q4"/>
+    <mergeCell ref="O5:Q5"/>
+    <mergeCell ref="O6:Q6"/>
+    <mergeCell ref="O7:Q7"/>
+    <mergeCell ref="O8:Q8"/>
+    <mergeCell ref="O9:Q9"/>
+    <mergeCell ref="O10:Q10"/>
+    <mergeCell ref="C45:N45"/>
+    <mergeCell ref="C46:N46"/>
+    <mergeCell ref="C47:N47"/>
+    <mergeCell ref="C48:N48"/>
+    <mergeCell ref="C49:N49"/>
+    <mergeCell ref="C50:N50"/>
+    <mergeCell ref="C39:N39"/>
+    <mergeCell ref="C15:N15"/>
+    <mergeCell ref="C16:N16"/>
+    <mergeCell ref="C17:N17"/>
+    <mergeCell ref="C18:N18"/>
+    <mergeCell ref="C19:N19"/>
+    <mergeCell ref="C20:N20"/>
+    <mergeCell ref="C35:N35"/>
+    <mergeCell ref="C40:N40"/>
+    <mergeCell ref="C41:N41"/>
+    <mergeCell ref="C42:N42"/>
+    <mergeCell ref="C43:N43"/>
+    <mergeCell ref="C44:N44"/>
+    <mergeCell ref="C33:N33"/>
+    <mergeCell ref="C34:N34"/>
+    <mergeCell ref="O17:Q17"/>
+    <mergeCell ref="O18:Q18"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O20:Q20"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O34:Q34"/>
+    <mergeCell ref="C38:N38"/>
+    <mergeCell ref="C27:N27"/>
+    <mergeCell ref="C28:N28"/>
+    <mergeCell ref="C29:N29"/>
+    <mergeCell ref="C30:N30"/>
+    <mergeCell ref="C31:N31"/>
+    <mergeCell ref="C32:N32"/>
+    <mergeCell ref="C36:N36"/>
+    <mergeCell ref="C37:N37"/>
+    <mergeCell ref="O11:Q11"/>
+    <mergeCell ref="O12:Q12"/>
+    <mergeCell ref="O13:Q13"/>
+    <mergeCell ref="O14:Q14"/>
+    <mergeCell ref="O15:Q15"/>
+    <mergeCell ref="O16:Q16"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O32:Q32"/>
+    <mergeCell ref="O33:Q33"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
     <mergeCell ref="O47:Q47"/>
     <mergeCell ref="O48:Q48"/>
     <mergeCell ref="O49:Q49"/>
@@ -1769,141 +1815,51 @@
     <mergeCell ref="O40:Q40"/>
     <mergeCell ref="O29:Q29"/>
     <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O11:Q11"/>
-    <mergeCell ref="O12:Q12"/>
-    <mergeCell ref="O13:Q13"/>
-    <mergeCell ref="O14:Q14"/>
-    <mergeCell ref="O15:Q15"/>
-    <mergeCell ref="O16:Q16"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O32:Q32"/>
-    <mergeCell ref="O33:Q33"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="C40:N40"/>
-    <mergeCell ref="C41:N41"/>
-    <mergeCell ref="C42:N42"/>
-    <mergeCell ref="C43:N43"/>
-    <mergeCell ref="C44:N44"/>
-    <mergeCell ref="C33:N33"/>
-    <mergeCell ref="C34:N34"/>
-    <mergeCell ref="O17:Q17"/>
-    <mergeCell ref="O18:Q18"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O20:Q20"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O34:Q34"/>
-    <mergeCell ref="C38:N38"/>
-    <mergeCell ref="C27:N27"/>
-    <mergeCell ref="C28:N28"/>
-    <mergeCell ref="C29:N29"/>
-    <mergeCell ref="C30:N30"/>
-    <mergeCell ref="C31:N31"/>
-    <mergeCell ref="C32:N32"/>
-    <mergeCell ref="C51:N51"/>
-    <mergeCell ref="O2:Q2"/>
-    <mergeCell ref="O3:Q3"/>
-    <mergeCell ref="O4:Q4"/>
-    <mergeCell ref="O5:Q5"/>
-    <mergeCell ref="O6:Q6"/>
-    <mergeCell ref="O7:Q7"/>
-    <mergeCell ref="O8:Q8"/>
-    <mergeCell ref="O9:Q9"/>
-    <mergeCell ref="O10:Q10"/>
-    <mergeCell ref="C45:N45"/>
-    <mergeCell ref="C46:N46"/>
-    <mergeCell ref="C47:N47"/>
-    <mergeCell ref="C48:N48"/>
-    <mergeCell ref="C49:N49"/>
-    <mergeCell ref="C50:N50"/>
-    <mergeCell ref="C39:N39"/>
-    <mergeCell ref="C15:N15"/>
-    <mergeCell ref="C16:N16"/>
-    <mergeCell ref="C17:N17"/>
-    <mergeCell ref="C18:N18"/>
-    <mergeCell ref="C19:N19"/>
-    <mergeCell ref="C20:N20"/>
-    <mergeCell ref="C35:N35"/>
-    <mergeCell ref="C36:N36"/>
-    <mergeCell ref="C37:N37"/>
-    <mergeCell ref="C14:N14"/>
-    <mergeCell ref="A49:B49"/>
-    <mergeCell ref="A50:B50"/>
-    <mergeCell ref="A51:B51"/>
-    <mergeCell ref="A45:B45"/>
-    <mergeCell ref="A46:B46"/>
-    <mergeCell ref="A47:B47"/>
-    <mergeCell ref="A48:B48"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="C21:N21"/>
-    <mergeCell ref="C22:N22"/>
-    <mergeCell ref="C23:N23"/>
-    <mergeCell ref="C24:N24"/>
-    <mergeCell ref="C25:N25"/>
-    <mergeCell ref="C26:N26"/>
-    <mergeCell ref="C7:N7"/>
-    <mergeCell ref="C8:N8"/>
-    <mergeCell ref="A43:B43"/>
-    <mergeCell ref="A44:B44"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="A41:B41"/>
-    <mergeCell ref="A42:B42"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="A35:B35"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C9:N9"/>
-    <mergeCell ref="C10:N10"/>
-    <mergeCell ref="C11:N11"/>
-    <mergeCell ref="C12:N12"/>
-    <mergeCell ref="C13:N13"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:N1"/>
-    <mergeCell ref="O1:Q1"/>
-    <mergeCell ref="R1:W1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C2:N2"/>
-    <mergeCell ref="C3:N3"/>
-    <mergeCell ref="C4:N4"/>
-    <mergeCell ref="C5:N5"/>
-    <mergeCell ref="C6:N6"/>
+    <mergeCell ref="R13:W13"/>
+    <mergeCell ref="R14:W14"/>
+    <mergeCell ref="R15:W15"/>
+    <mergeCell ref="R16:W16"/>
+    <mergeCell ref="R17:W17"/>
+    <mergeCell ref="R18:W18"/>
+    <mergeCell ref="R7:W7"/>
+    <mergeCell ref="R8:W8"/>
+    <mergeCell ref="R9:W9"/>
+    <mergeCell ref="R10:W10"/>
+    <mergeCell ref="R11:W11"/>
+    <mergeCell ref="R12:W12"/>
+    <mergeCell ref="R25:W25"/>
+    <mergeCell ref="R26:W26"/>
+    <mergeCell ref="R27:W27"/>
+    <mergeCell ref="R28:W28"/>
+    <mergeCell ref="R29:W29"/>
+    <mergeCell ref="R30:W30"/>
+    <mergeCell ref="R19:W19"/>
+    <mergeCell ref="R20:W20"/>
+    <mergeCell ref="R21:W21"/>
+    <mergeCell ref="R22:W22"/>
+    <mergeCell ref="R23:W23"/>
+    <mergeCell ref="R24:W24"/>
+    <mergeCell ref="R37:W37"/>
+    <mergeCell ref="R38:W38"/>
+    <mergeCell ref="R39:W39"/>
+    <mergeCell ref="R40:W40"/>
+    <mergeCell ref="R41:W41"/>
+    <mergeCell ref="R42:W42"/>
+    <mergeCell ref="R31:W31"/>
+    <mergeCell ref="R32:W32"/>
+    <mergeCell ref="R33:W33"/>
+    <mergeCell ref="R34:W34"/>
+    <mergeCell ref="R35:W35"/>
+    <mergeCell ref="R36:W36"/>
+    <mergeCell ref="R49:W49"/>
+    <mergeCell ref="R50:W50"/>
+    <mergeCell ref="R51:W51"/>
+    <mergeCell ref="R43:W43"/>
+    <mergeCell ref="R44:W44"/>
+    <mergeCell ref="R45:W45"/>
+    <mergeCell ref="R46:W46"/>
+    <mergeCell ref="R47:W47"/>
+    <mergeCell ref="R48:W48"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
